--- a/Cardiologie/Excel/cardio_15.xlsx
+++ b/Cardiologie/Excel/cardio_15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3C7068-D622-43EF-9AD0-D2146317FB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649007BA-9893-44D7-8318-D0C4960F27F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,16 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="248">
-  <si>
-    <t>numero</t>
-  </si>
-  <si>
-    <t>proposition</t>
-  </si>
-  <si>
-    <t>reponse</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
   <si>
     <t>La TVP est toujours définie comme une thrombose complète du réseau veineux profond des MI.</t>
   </si>
@@ -757,29 +748,36 @@
     <t>Les AVK sont parfois utilisés dans le traitement des TVS étendues pros de la jonction saphéno-fémorale.</t>
   </si>
   <si>
-    <t>Faux</t>
-  </si>
-  <si>
-    <t>Vrai</t>
-  </si>
-  <si>
     <t>La TVP distale est limitée à l'étage poplité.</t>
+  </si>
+  <si>
+    <t>Numero</t>
+  </si>
+  <si>
+    <t>Proposition</t>
+  </si>
+  <si>
+    <t>Reponse</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>image</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -795,27 +793,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -824,8 +807,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1131,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C244"/>
+  <dimension ref="A1:G244"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -1139,180 +1122,192 @@
     <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="C15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>245</v>
+        <v>13</v>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1320,10 +1315,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>246</v>
+        <v>14</v>
+      </c>
+      <c r="C17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1331,10 +1326,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" t="s">
-        <v>245</v>
+        <v>15</v>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1342,10 +1337,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" t="s">
-        <v>246</v>
+        <v>16</v>
+      </c>
+      <c r="C19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1353,10 +1348,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>245</v>
+        <v>17</v>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1364,10 +1359,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
-        <v>246</v>
+        <v>18</v>
+      </c>
+      <c r="C21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1375,10 +1370,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>245</v>
+        <v>19</v>
+      </c>
+      <c r="C22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1386,10 +1381,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
-        <v>246</v>
+        <v>20</v>
+      </c>
+      <c r="C23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1397,10 +1392,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" t="s">
-        <v>246</v>
+        <v>21</v>
+      </c>
+      <c r="C24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1408,10 +1403,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" t="s">
-        <v>245</v>
+        <v>22</v>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1419,10 +1414,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" t="s">
-        <v>246</v>
+        <v>23</v>
+      </c>
+      <c r="C26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1430,10 +1425,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" t="s">
-        <v>246</v>
+        <v>24</v>
+      </c>
+      <c r="C27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1441,10 +1436,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" t="s">
-        <v>245</v>
+        <v>25</v>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1452,10 +1447,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" t="s">
-        <v>246</v>
+        <v>26</v>
+      </c>
+      <c r="C29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1463,10 +1458,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" t="s">
-        <v>246</v>
+        <v>27</v>
+      </c>
+      <c r="C30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1474,10 +1469,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" t="s">
-        <v>245</v>
+        <v>28</v>
+      </c>
+      <c r="C31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1485,10 +1480,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" t="s">
-        <v>245</v>
+        <v>29</v>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1496,10 +1491,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" t="s">
-        <v>245</v>
+        <v>30</v>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1507,10 +1502,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" t="s">
-        <v>245</v>
+        <v>31</v>
+      </c>
+      <c r="C34" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1518,10 +1513,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" t="s">
-        <v>246</v>
+        <v>32</v>
+      </c>
+      <c r="C35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1529,10 +1524,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" t="s">
-        <v>245</v>
+        <v>33</v>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1540,10 +1535,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" t="s">
-        <v>246</v>
+        <v>34</v>
+      </c>
+      <c r="C37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1551,10 +1546,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" t="s">
-        <v>245</v>
+        <v>35</v>
+      </c>
+      <c r="C38" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1562,10 +1557,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C39" t="s">
-        <v>246</v>
+        <v>36</v>
+      </c>
+      <c r="C39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1573,10 +1568,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" t="s">
-        <v>245</v>
+        <v>37</v>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1584,10 +1579,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" t="s">
-        <v>245</v>
+        <v>38</v>
+      </c>
+      <c r="C41" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1595,10 +1590,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" t="s">
-        <v>245</v>
+        <v>39</v>
+      </c>
+      <c r="C42" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1606,10 +1601,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" t="s">
-        <v>245</v>
+        <v>40</v>
+      </c>
+      <c r="C43" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1617,10 +1612,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" t="s">
-        <v>245</v>
+        <v>41</v>
+      </c>
+      <c r="C44" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1628,10 +1623,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" t="s">
-        <v>245</v>
+        <v>42</v>
+      </c>
+      <c r="C45" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1639,10 +1634,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" t="s">
-        <v>246</v>
+        <v>43</v>
+      </c>
+      <c r="C46" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1650,10 +1645,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" t="s">
-        <v>246</v>
+        <v>44</v>
+      </c>
+      <c r="C47" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1661,10 +1656,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
-      </c>
-      <c r="C48" t="s">
-        <v>246</v>
+        <v>45</v>
+      </c>
+      <c r="C48" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1672,10 +1667,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49" t="s">
-        <v>245</v>
+        <v>46</v>
+      </c>
+      <c r="C49" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1683,10 +1678,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
-      </c>
-      <c r="C50" t="s">
-        <v>245</v>
+        <v>47</v>
+      </c>
+      <c r="C50" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1694,10 +1689,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
-      </c>
-      <c r="C51" t="s">
-        <v>246</v>
+        <v>48</v>
+      </c>
+      <c r="C51" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1705,10 +1700,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
-      </c>
-      <c r="C52" t="s">
-        <v>245</v>
+        <v>49</v>
+      </c>
+      <c r="C52" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1716,10 +1711,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" t="s">
-        <v>245</v>
+        <v>50</v>
+      </c>
+      <c r="C53" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1727,10 +1722,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
-      </c>
-      <c r="C54" t="s">
-        <v>246</v>
+        <v>51</v>
+      </c>
+      <c r="C54" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1738,10 +1733,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
-      </c>
-      <c r="C55" t="s">
-        <v>246</v>
+        <v>52</v>
+      </c>
+      <c r="C55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1749,10 +1744,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
-      </c>
-      <c r="C56" t="s">
-        <v>245</v>
+        <v>53</v>
+      </c>
+      <c r="C56" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1760,10 +1755,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" t="s">
-        <v>245</v>
+        <v>54</v>
+      </c>
+      <c r="C57" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1771,10 +1766,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
-      </c>
-      <c r="C58" t="s">
-        <v>245</v>
+        <v>55</v>
+      </c>
+      <c r="C58" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1782,10 +1777,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" t="s">
-        <v>246</v>
+        <v>56</v>
+      </c>
+      <c r="C59" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1793,10 +1788,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
-      </c>
-      <c r="C60" t="s">
-        <v>245</v>
+        <v>57</v>
+      </c>
+      <c r="C60" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1804,10 +1799,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" t="s">
-        <v>245</v>
+        <v>58</v>
+      </c>
+      <c r="C61" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1815,10 +1810,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
-      </c>
-      <c r="C62" t="s">
-        <v>246</v>
+        <v>59</v>
+      </c>
+      <c r="C62" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1826,10 +1821,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
-      </c>
-      <c r="C63" t="s">
-        <v>245</v>
+        <v>60</v>
+      </c>
+      <c r="C63" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1837,10 +1832,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
-      </c>
-      <c r="C64" t="s">
-        <v>246</v>
+        <v>61</v>
+      </c>
+      <c r="C64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1848,10 +1843,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
-      </c>
-      <c r="C65" t="s">
-        <v>246</v>
+        <v>62</v>
+      </c>
+      <c r="C65" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1859,10 +1854,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
-      </c>
-      <c r="C66" t="s">
-        <v>246</v>
+        <v>63</v>
+      </c>
+      <c r="C66" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1870,10 +1865,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
-      </c>
-      <c r="C67" t="s">
-        <v>245</v>
+        <v>64</v>
+      </c>
+      <c r="C67" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1881,10 +1876,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
-      </c>
-      <c r="C68" t="s">
-        <v>245</v>
+        <v>65</v>
+      </c>
+      <c r="C68" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1892,10 +1887,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" t="s">
-        <v>246</v>
+        <v>66</v>
+      </c>
+      <c r="C69" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1903,10 +1898,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
-      </c>
-      <c r="C70" t="s">
-        <v>245</v>
+        <v>67</v>
+      </c>
+      <c r="C70" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1914,10 +1909,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
-      </c>
-      <c r="C71" t="s">
-        <v>245</v>
+        <v>68</v>
+      </c>
+      <c r="C71" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1925,10 +1920,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
-      </c>
-      <c r="C72" t="s">
-        <v>246</v>
+        <v>69</v>
+      </c>
+      <c r="C72" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1936,10 +1931,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
-      </c>
-      <c r="C73" t="s">
-        <v>246</v>
+        <v>70</v>
+      </c>
+      <c r="C73" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1947,10 +1942,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
-      </c>
-      <c r="C74" t="s">
-        <v>246</v>
+        <v>71</v>
+      </c>
+      <c r="C74" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -1958,10 +1953,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
-      </c>
-      <c r="C75" t="s">
-        <v>246</v>
+        <v>72</v>
+      </c>
+      <c r="C75" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1969,10 +1964,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
-      </c>
-      <c r="C76" t="s">
-        <v>246</v>
+        <v>73</v>
+      </c>
+      <c r="C76" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1980,10 +1975,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
-      </c>
-      <c r="C77" t="s">
-        <v>245</v>
+        <v>74</v>
+      </c>
+      <c r="C77" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1991,10 +1986,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
-      </c>
-      <c r="C78" t="s">
-        <v>245</v>
+        <v>75</v>
+      </c>
+      <c r="C78" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2002,10 +1997,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
-      </c>
-      <c r="C79" t="s">
-        <v>246</v>
+        <v>76</v>
+      </c>
+      <c r="C79" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -2013,10 +2008,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
-      </c>
-      <c r="C80" t="s">
-        <v>246</v>
+        <v>77</v>
+      </c>
+      <c r="C80" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2024,10 +2019,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
-      </c>
-      <c r="C81" t="s">
-        <v>246</v>
+        <v>78</v>
+      </c>
+      <c r="C81" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2035,10 +2030,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
-      </c>
-      <c r="C82" t="s">
-        <v>245</v>
+        <v>79</v>
+      </c>
+      <c r="C82" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2046,10 +2041,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
-      </c>
-      <c r="C83" t="s">
-        <v>245</v>
+        <v>80</v>
+      </c>
+      <c r="C83" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2057,10 +2052,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
-      </c>
-      <c r="C84" t="s">
-        <v>245</v>
+        <v>81</v>
+      </c>
+      <c r="C84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2068,10 +2063,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
-      </c>
-      <c r="C85" t="s">
-        <v>246</v>
+        <v>82</v>
+      </c>
+      <c r="C85" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2079,10 +2074,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
-      </c>
-      <c r="C86" t="s">
-        <v>246</v>
+        <v>83</v>
+      </c>
+      <c r="C86" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2090,10 +2085,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
-      </c>
-      <c r="C87" t="s">
-        <v>245</v>
+        <v>84</v>
+      </c>
+      <c r="C87" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2101,10 +2096,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
-      </c>
-      <c r="C88" t="s">
-        <v>245</v>
+        <v>85</v>
+      </c>
+      <c r="C88" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2112,10 +2107,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
-      </c>
-      <c r="C89" t="s">
-        <v>245</v>
+        <v>86</v>
+      </c>
+      <c r="C89" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2123,10 +2118,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
-      </c>
-      <c r="C90" t="s">
-        <v>246</v>
+        <v>87</v>
+      </c>
+      <c r="C90" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2134,10 +2129,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
-      </c>
-      <c r="C91" t="s">
-        <v>246</v>
+        <v>88</v>
+      </c>
+      <c r="C91" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2145,10 +2140,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
-      </c>
-      <c r="C92" t="s">
-        <v>246</v>
+        <v>89</v>
+      </c>
+      <c r="C92" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -2156,10 +2151,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
-      </c>
-      <c r="C93" t="s">
-        <v>246</v>
+        <v>90</v>
+      </c>
+      <c r="C93" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -2167,10 +2162,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
-      </c>
-      <c r="C94" t="s">
-        <v>245</v>
+        <v>91</v>
+      </c>
+      <c r="C94" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -2178,10 +2173,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
-      </c>
-      <c r="C95" t="s">
-        <v>245</v>
+        <v>92</v>
+      </c>
+      <c r="C95" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2189,10 +2184,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
-      </c>
-      <c r="C96" t="s">
-        <v>246</v>
+        <v>93</v>
+      </c>
+      <c r="C96" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2200,10 +2195,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
-      </c>
-      <c r="C97" t="s">
-        <v>246</v>
+        <v>94</v>
+      </c>
+      <c r="C97" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2211,10 +2206,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
-      </c>
-      <c r="C98" t="s">
-        <v>246</v>
+        <v>95</v>
+      </c>
+      <c r="C98" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2222,10 +2217,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
-      </c>
-      <c r="C99" t="s">
-        <v>245</v>
+        <v>96</v>
+      </c>
+      <c r="C99" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2233,10 +2228,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
-      </c>
-      <c r="C100" t="s">
-        <v>246</v>
+        <v>97</v>
+      </c>
+      <c r="C100" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2244,10 +2239,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
-      </c>
-      <c r="C101" t="s">
-        <v>246</v>
+        <v>98</v>
+      </c>
+      <c r="C101" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2255,10 +2250,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
-      </c>
-      <c r="C102" t="s">
-        <v>245</v>
+        <v>99</v>
+      </c>
+      <c r="C102" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2266,10 +2261,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
-      </c>
-      <c r="C103" t="s">
-        <v>246</v>
+        <v>100</v>
+      </c>
+      <c r="C103" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2277,10 +2272,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
-      </c>
-      <c r="C104" t="s">
-        <v>246</v>
+        <v>101</v>
+      </c>
+      <c r="C104" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -2288,10 +2283,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
-      </c>
-      <c r="C105" t="s">
-        <v>245</v>
+        <v>102</v>
+      </c>
+      <c r="C105" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2299,10 +2294,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
-      </c>
-      <c r="C106" t="s">
-        <v>245</v>
+        <v>103</v>
+      </c>
+      <c r="C106" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2310,10 +2305,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
-      </c>
-      <c r="C107" t="s">
-        <v>246</v>
+        <v>104</v>
+      </c>
+      <c r="C107" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2321,10 +2316,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
-      </c>
-      <c r="C108" t="s">
-        <v>246</v>
+        <v>105</v>
+      </c>
+      <c r="C108" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2332,10 +2327,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
-      </c>
-      <c r="C109" t="s">
-        <v>246</v>
+        <v>106</v>
+      </c>
+      <c r="C109" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -2343,10 +2338,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
-      </c>
-      <c r="C110" t="s">
-        <v>245</v>
+        <v>107</v>
+      </c>
+      <c r="C110" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2354,10 +2349,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
-      </c>
-      <c r="C111" t="s">
-        <v>246</v>
+        <v>108</v>
+      </c>
+      <c r="C111" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -2365,10 +2360,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
-      </c>
-      <c r="C112" t="s">
-        <v>245</v>
+        <v>109</v>
+      </c>
+      <c r="C112" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -2376,10 +2371,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
-      </c>
-      <c r="C113" t="s">
-        <v>246</v>
+        <v>110</v>
+      </c>
+      <c r="C113" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -2387,10 +2382,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
-      </c>
-      <c r="C114" t="s">
-        <v>245</v>
+        <v>111</v>
+      </c>
+      <c r="C114" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -2398,10 +2393,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
-      </c>
-      <c r="C115" t="s">
-        <v>245</v>
+        <v>112</v>
+      </c>
+      <c r="C115" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -2409,10 +2404,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
-      </c>
-      <c r="C116" t="s">
-        <v>246</v>
+        <v>113</v>
+      </c>
+      <c r="C116" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -2420,10 +2415,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
-      </c>
-      <c r="C117" t="s">
-        <v>245</v>
+        <v>114</v>
+      </c>
+      <c r="C117" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -2431,10 +2426,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
-      </c>
-      <c r="C118" t="s">
-        <v>246</v>
+        <v>115</v>
+      </c>
+      <c r="C118" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -2442,10 +2437,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
-      </c>
-      <c r="C119" t="s">
-        <v>246</v>
+        <v>116</v>
+      </c>
+      <c r="C119" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -2453,10 +2448,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
-      </c>
-      <c r="C120" t="s">
-        <v>245</v>
+        <v>117</v>
+      </c>
+      <c r="C120" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -2464,10 +2459,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
-      </c>
-      <c r="C121" t="s">
-        <v>245</v>
+        <v>118</v>
+      </c>
+      <c r="C121" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -2475,10 +2470,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
-      </c>
-      <c r="C122" t="s">
-        <v>246</v>
+        <v>119</v>
+      </c>
+      <c r="C122" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -2486,10 +2481,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
-      </c>
-      <c r="C123" t="s">
-        <v>245</v>
+        <v>120</v>
+      </c>
+      <c r="C123" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -2497,10 +2492,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
-      </c>
-      <c r="C124" t="s">
-        <v>245</v>
+        <v>121</v>
+      </c>
+      <c r="C124" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -2508,10 +2503,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
-      </c>
-      <c r="C125" t="s">
-        <v>245</v>
+        <v>122</v>
+      </c>
+      <c r="C125" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -2519,10 +2514,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
-      </c>
-      <c r="C126" t="s">
-        <v>246</v>
+        <v>123</v>
+      </c>
+      <c r="C126" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -2530,10 +2525,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
-      </c>
-      <c r="C127" t="s">
-        <v>245</v>
+        <v>124</v>
+      </c>
+      <c r="C127" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2541,10 +2536,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
-      </c>
-      <c r="C128" t="s">
-        <v>246</v>
+        <v>125</v>
+      </c>
+      <c r="C128" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -2552,10 +2547,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
-      </c>
-      <c r="C129" t="s">
-        <v>245</v>
+        <v>126</v>
+      </c>
+      <c r="C129" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -2563,10 +2558,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
-      </c>
-      <c r="C130" t="s">
-        <v>245</v>
+        <v>127</v>
+      </c>
+      <c r="C130" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -2574,10 +2569,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
-      </c>
-      <c r="C131" t="s">
-        <v>245</v>
+        <v>128</v>
+      </c>
+      <c r="C131" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -2585,10 +2580,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
-      </c>
-      <c r="C132" t="s">
-        <v>245</v>
+        <v>129</v>
+      </c>
+      <c r="C132" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -2596,10 +2591,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
-      </c>
-      <c r="C133" t="s">
-        <v>246</v>
+        <v>130</v>
+      </c>
+      <c r="C133" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -2607,10 +2602,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
-      </c>
-      <c r="C134" t="s">
-        <v>246</v>
+        <v>131</v>
+      </c>
+      <c r="C134" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -2618,10 +2613,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
-      </c>
-      <c r="C135" t="s">
-        <v>245</v>
+        <v>132</v>
+      </c>
+      <c r="C135" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -2629,10 +2624,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
-      </c>
-      <c r="C136" t="s">
-        <v>246</v>
+        <v>133</v>
+      </c>
+      <c r="C136" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -2640,10 +2635,10 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
-      </c>
-      <c r="C137" t="s">
-        <v>246</v>
+        <v>134</v>
+      </c>
+      <c r="C137" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -2651,10 +2646,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
-      </c>
-      <c r="C138" t="s">
-        <v>246</v>
+        <v>135</v>
+      </c>
+      <c r="C138" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -2662,10 +2657,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
-      </c>
-      <c r="C139" t="s">
-        <v>246</v>
+        <v>136</v>
+      </c>
+      <c r="C139" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -2673,10 +2668,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
-      </c>
-      <c r="C140" t="s">
-        <v>245</v>
+        <v>137</v>
+      </c>
+      <c r="C140" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -2684,10 +2679,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
-      </c>
-      <c r="C141" t="s">
-        <v>246</v>
+        <v>138</v>
+      </c>
+      <c r="C141" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -2695,10 +2690,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
-      </c>
-      <c r="C142" t="s">
-        <v>245</v>
+        <v>139</v>
+      </c>
+      <c r="C142" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -2706,10 +2701,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
-      </c>
-      <c r="C143" t="s">
-        <v>246</v>
+        <v>140</v>
+      </c>
+      <c r="C143" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -2717,10 +2712,10 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
-      </c>
-      <c r="C144" t="s">
-        <v>245</v>
+        <v>141</v>
+      </c>
+      <c r="C144" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -2728,10 +2723,10 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
-      </c>
-      <c r="C145" t="s">
-        <v>245</v>
+        <v>142</v>
+      </c>
+      <c r="C145" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -2739,10 +2734,10 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
-      </c>
-      <c r="C146" t="s">
-        <v>246</v>
+        <v>143</v>
+      </c>
+      <c r="C146" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -2750,10 +2745,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
-      </c>
-      <c r="C147" t="s">
-        <v>246</v>
+        <v>144</v>
+      </c>
+      <c r="C147" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -2761,10 +2756,10 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
-      </c>
-      <c r="C148" t="s">
-        <v>246</v>
+        <v>145</v>
+      </c>
+      <c r="C148" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -2772,10 +2767,10 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
-      </c>
-      <c r="C149" t="s">
-        <v>245</v>
+        <v>146</v>
+      </c>
+      <c r="C149" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -2783,10 +2778,10 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
-      </c>
-      <c r="C150" t="s">
-        <v>246</v>
+        <v>147</v>
+      </c>
+      <c r="C150" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -2794,10 +2789,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
-      </c>
-      <c r="C151" t="s">
-        <v>246</v>
+        <v>148</v>
+      </c>
+      <c r="C151" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -2805,10 +2800,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
-      </c>
-      <c r="C152" t="s">
-        <v>246</v>
+        <v>149</v>
+      </c>
+      <c r="C152" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -2816,10 +2811,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
-      </c>
-      <c r="C153" t="s">
-        <v>246</v>
+        <v>150</v>
+      </c>
+      <c r="C153" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -2827,10 +2822,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
-      </c>
-      <c r="C154" t="s">
-        <v>245</v>
+        <v>151</v>
+      </c>
+      <c r="C154" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -2838,10 +2833,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
-      </c>
-      <c r="C155" t="s">
-        <v>245</v>
+        <v>152</v>
+      </c>
+      <c r="C155" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -2849,10 +2844,10 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
-      </c>
-      <c r="C156" t="s">
-        <v>245</v>
+        <v>153</v>
+      </c>
+      <c r="C156" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -2860,10 +2855,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
-      </c>
-      <c r="C157" t="s">
-        <v>246</v>
+        <v>154</v>
+      </c>
+      <c r="C157" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -2871,10 +2866,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
-      </c>
-      <c r="C158" t="s">
-        <v>246</v>
+        <v>155</v>
+      </c>
+      <c r="C158" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -2882,10 +2877,10 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
-      </c>
-      <c r="C159" t="s">
-        <v>245</v>
+        <v>156</v>
+      </c>
+      <c r="C159" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -2893,10 +2888,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
-      </c>
-      <c r="C160" t="s">
-        <v>246</v>
+        <v>157</v>
+      </c>
+      <c r="C160" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -2904,10 +2899,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
-      </c>
-      <c r="C161" t="s">
-        <v>246</v>
+        <v>158</v>
+      </c>
+      <c r="C161" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -2915,10 +2910,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
-      </c>
-      <c r="C162" t="s">
-        <v>245</v>
+        <v>159</v>
+      </c>
+      <c r="C162" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -2926,10 +2921,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
-      </c>
-      <c r="C163" t="s">
-        <v>245</v>
+        <v>160</v>
+      </c>
+      <c r="C163" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -2937,10 +2932,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
-      </c>
-      <c r="C164" t="s">
-        <v>246</v>
+        <v>161</v>
+      </c>
+      <c r="C164" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -2948,10 +2943,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
-      </c>
-      <c r="C165" t="s">
-        <v>246</v>
+        <v>162</v>
+      </c>
+      <c r="C165" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -2959,10 +2954,10 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
-      </c>
-      <c r="C166" t="s">
-        <v>245</v>
+        <v>163</v>
+      </c>
+      <c r="C166" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -2970,10 +2965,10 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
-      </c>
-      <c r="C167" t="s">
-        <v>246</v>
+        <v>164</v>
+      </c>
+      <c r="C167" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -2981,10 +2976,10 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
-      </c>
-      <c r="C168" t="s">
-        <v>245</v>
+        <v>165</v>
+      </c>
+      <c r="C168" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -2992,10 +2987,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
-      </c>
-      <c r="C169" t="s">
-        <v>246</v>
+        <v>166</v>
+      </c>
+      <c r="C169" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -3003,10 +2998,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
-      </c>
-      <c r="C170" t="s">
-        <v>246</v>
+        <v>167</v>
+      </c>
+      <c r="C170" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -3014,10 +3009,10 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
-      </c>
-      <c r="C171" t="s">
-        <v>245</v>
+        <v>168</v>
+      </c>
+      <c r="C171" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -3025,10 +3020,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
-      </c>
-      <c r="C172" t="s">
-        <v>245</v>
+        <v>169</v>
+      </c>
+      <c r="C172" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -3036,10 +3031,10 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
-      </c>
-      <c r="C173" t="s">
-        <v>245</v>
+        <v>170</v>
+      </c>
+      <c r="C173" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -3047,10 +3042,10 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
-      </c>
-      <c r="C174" t="s">
-        <v>246</v>
+        <v>171</v>
+      </c>
+      <c r="C174" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -3058,10 +3053,10 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
-      </c>
-      <c r="C175" t="s">
-        <v>245</v>
+        <v>172</v>
+      </c>
+      <c r="C175" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -3069,10 +3064,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
-      </c>
-      <c r="C176" t="s">
-        <v>245</v>
+        <v>173</v>
+      </c>
+      <c r="C176" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -3080,10 +3075,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
-      </c>
-      <c r="C177" t="s">
-        <v>246</v>
+        <v>174</v>
+      </c>
+      <c r="C177" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -3091,10 +3086,10 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
-      </c>
-      <c r="C178" t="s">
-        <v>245</v>
+        <v>175</v>
+      </c>
+      <c r="C178" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -3102,10 +3097,10 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
-      </c>
-      <c r="C179" t="s">
-        <v>246</v>
+        <v>176</v>
+      </c>
+      <c r="C179" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -3113,10 +3108,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
-      </c>
-      <c r="C180" t="s">
-        <v>245</v>
+        <v>177</v>
+      </c>
+      <c r="C180" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -3124,10 +3119,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
-      </c>
-      <c r="C181" t="s">
-        <v>246</v>
+        <v>178</v>
+      </c>
+      <c r="C181" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -3135,10 +3130,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
-      </c>
-      <c r="C182" t="s">
-        <v>245</v>
+        <v>179</v>
+      </c>
+      <c r="C182" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -3146,10 +3141,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
-      </c>
-      <c r="C183" t="s">
-        <v>246</v>
+        <v>180</v>
+      </c>
+      <c r="C183" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -3157,10 +3152,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
-      </c>
-      <c r="C184" t="s">
-        <v>245</v>
+        <v>181</v>
+      </c>
+      <c r="C184" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -3168,10 +3163,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
-      </c>
-      <c r="C185" t="s">
-        <v>245</v>
+        <v>182</v>
+      </c>
+      <c r="C185" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -3179,10 +3174,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
-      </c>
-      <c r="C186" t="s">
-        <v>246</v>
+        <v>183</v>
+      </c>
+      <c r="C186" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -3190,10 +3185,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
-      </c>
-      <c r="C187" t="s">
-        <v>245</v>
+        <v>184</v>
+      </c>
+      <c r="C187" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -3201,10 +3196,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
-      </c>
-      <c r="C188" t="s">
-        <v>246</v>
+        <v>185</v>
+      </c>
+      <c r="C188" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -3212,10 +3207,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
-      </c>
-      <c r="C189" t="s">
-        <v>245</v>
+        <v>186</v>
+      </c>
+      <c r="C189" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -3223,10 +3218,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
-      </c>
-      <c r="C190" t="s">
-        <v>245</v>
+        <v>187</v>
+      </c>
+      <c r="C190" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -3234,10 +3229,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
-      </c>
-      <c r="C191" t="s">
-        <v>246</v>
+        <v>188</v>
+      </c>
+      <c r="C191" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -3245,10 +3240,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
-      </c>
-      <c r="C192" t="s">
-        <v>246</v>
+        <v>189</v>
+      </c>
+      <c r="C192" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -3256,10 +3251,10 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
-      </c>
-      <c r="C193" t="s">
-        <v>246</v>
+        <v>190</v>
+      </c>
+      <c r="C193" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -3267,10 +3262,10 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
-      </c>
-      <c r="C194" t="s">
-        <v>245</v>
+        <v>191</v>
+      </c>
+      <c r="C194" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -3278,10 +3273,10 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
-      </c>
-      <c r="C195" t="s">
-        <v>245</v>
+        <v>192</v>
+      </c>
+      <c r="C195" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -3289,10 +3284,10 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
-      </c>
-      <c r="C196" t="s">
-        <v>246</v>
+        <v>193</v>
+      </c>
+      <c r="C196" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -3300,10 +3295,10 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
-      </c>
-      <c r="C197" t="s">
-        <v>246</v>
+        <v>194</v>
+      </c>
+      <c r="C197" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -3311,10 +3306,10 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
-      </c>
-      <c r="C198" t="s">
-        <v>245</v>
+        <v>195</v>
+      </c>
+      <c r="C198" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -3322,10 +3317,10 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
-      </c>
-      <c r="C199" t="s">
-        <v>246</v>
+        <v>196</v>
+      </c>
+      <c r="C199" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -3333,10 +3328,10 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
-      </c>
-      <c r="C200" t="s">
-        <v>245</v>
+        <v>197</v>
+      </c>
+      <c r="C200" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -3344,10 +3339,10 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
-      </c>
-      <c r="C201" t="s">
-        <v>246</v>
+        <v>198</v>
+      </c>
+      <c r="C201" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -3355,10 +3350,10 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
-      </c>
-      <c r="C202" t="s">
-        <v>246</v>
+        <v>199</v>
+      </c>
+      <c r="C202" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -3366,10 +3361,10 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
-      </c>
-      <c r="C203" t="s">
-        <v>245</v>
+        <v>200</v>
+      </c>
+      <c r="C203" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -3377,10 +3372,10 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
-      </c>
-      <c r="C204" t="s">
-        <v>245</v>
+        <v>201</v>
+      </c>
+      <c r="C204" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -3388,10 +3383,10 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
-      </c>
-      <c r="C205" t="s">
-        <v>246</v>
+        <v>202</v>
+      </c>
+      <c r="C205" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -3399,10 +3394,10 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
-      </c>
-      <c r="C206" t="s">
-        <v>246</v>
+        <v>203</v>
+      </c>
+      <c r="C206" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -3410,10 +3405,10 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
-      </c>
-      <c r="C207" t="s">
-        <v>246</v>
+        <v>204</v>
+      </c>
+      <c r="C207" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -3421,10 +3416,10 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
-      </c>
-      <c r="C208" t="s">
-        <v>245</v>
+        <v>205</v>
+      </c>
+      <c r="C208" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -3432,10 +3427,10 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
-      </c>
-      <c r="C209" t="s">
-        <v>246</v>
+        <v>206</v>
+      </c>
+      <c r="C209" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -3443,10 +3438,10 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
-      </c>
-      <c r="C210" t="s">
-        <v>245</v>
+        <v>207</v>
+      </c>
+      <c r="C210" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -3454,10 +3449,10 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
-      </c>
-      <c r="C211" t="s">
-        <v>245</v>
+        <v>208</v>
+      </c>
+      <c r="C211" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -3465,10 +3460,10 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
-      </c>
-      <c r="C212" t="s">
-        <v>246</v>
+        <v>209</v>
+      </c>
+      <c r="C212" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -3476,10 +3471,10 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
-      </c>
-      <c r="C213" t="s">
-        <v>245</v>
+        <v>210</v>
+      </c>
+      <c r="C213" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -3487,10 +3482,10 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
-      </c>
-      <c r="C214" t="s">
-        <v>246</v>
+        <v>211</v>
+      </c>
+      <c r="C214" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -3498,10 +3493,10 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
-      </c>
-      <c r="C215" t="s">
-        <v>245</v>
+        <v>212</v>
+      </c>
+      <c r="C215" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -3509,10 +3504,10 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
-      </c>
-      <c r="C216" t="s">
-        <v>246</v>
+        <v>213</v>
+      </c>
+      <c r="C216" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -3520,10 +3515,10 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
-      </c>
-      <c r="C217" t="s">
-        <v>246</v>
+        <v>214</v>
+      </c>
+      <c r="C217" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -3531,10 +3526,10 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
-      </c>
-      <c r="C218" t="s">
-        <v>245</v>
+        <v>215</v>
+      </c>
+      <c r="C218" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -3542,10 +3537,10 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
-      </c>
-      <c r="C219" t="s">
-        <v>245</v>
+        <v>216</v>
+      </c>
+      <c r="C219" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -3553,10 +3548,10 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
-      </c>
-      <c r="C220" t="s">
-        <v>246</v>
+        <v>217</v>
+      </c>
+      <c r="C220" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -3564,10 +3559,10 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
-      </c>
-      <c r="C221" t="s">
-        <v>245</v>
+        <v>218</v>
+      </c>
+      <c r="C221" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -3575,10 +3570,10 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
-      </c>
-      <c r="C222" t="s">
-        <v>246</v>
+        <v>219</v>
+      </c>
+      <c r="C222" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -3586,10 +3581,10 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
-      </c>
-      <c r="C223" t="s">
-        <v>245</v>
+        <v>220</v>
+      </c>
+      <c r="C223" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -3597,10 +3592,10 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
-      </c>
-      <c r="C224" t="s">
-        <v>245</v>
+        <v>221</v>
+      </c>
+      <c r="C224" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -3608,10 +3603,10 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
-      </c>
-      <c r="C225" t="s">
-        <v>246</v>
+        <v>222</v>
+      </c>
+      <c r="C225" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -3619,10 +3614,10 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
-      </c>
-      <c r="C226" t="s">
-        <v>246</v>
+        <v>223</v>
+      </c>
+      <c r="C226" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -3630,10 +3625,10 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
-      </c>
-      <c r="C227" t="s">
-        <v>245</v>
+        <v>224</v>
+      </c>
+      <c r="C227" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -3641,10 +3636,10 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
-      </c>
-      <c r="C228" t="s">
-        <v>246</v>
+        <v>225</v>
+      </c>
+      <c r="C228" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -3652,10 +3647,10 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
-      </c>
-      <c r="C229" t="s">
-        <v>246</v>
+        <v>226</v>
+      </c>
+      <c r="C229" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -3663,10 +3658,10 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
-      </c>
-      <c r="C230" t="s">
-        <v>245</v>
+        <v>227</v>
+      </c>
+      <c r="C230" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -3674,10 +3669,10 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
-      </c>
-      <c r="C231" t="s">
-        <v>245</v>
+        <v>228</v>
+      </c>
+      <c r="C231" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -3685,10 +3680,10 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
-      </c>
-      <c r="C232" t="s">
-        <v>245</v>
+        <v>229</v>
+      </c>
+      <c r="C232" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -3696,10 +3691,10 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
-      </c>
-      <c r="C233" t="s">
-        <v>246</v>
+        <v>230</v>
+      </c>
+      <c r="C233" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -3707,10 +3702,10 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
-      </c>
-      <c r="C234" t="s">
-        <v>245</v>
+        <v>231</v>
+      </c>
+      <c r="C234" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -3718,10 +3713,10 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
-      </c>
-      <c r="C235" t="s">
-        <v>246</v>
+        <v>232</v>
+      </c>
+      <c r="C235" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -3729,10 +3724,10 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
-      </c>
-      <c r="C236" t="s">
-        <v>246</v>
+        <v>233</v>
+      </c>
+      <c r="C236" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -3740,10 +3735,10 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
-      </c>
-      <c r="C237" t="s">
-        <v>246</v>
+        <v>234</v>
+      </c>
+      <c r="C237" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -3751,10 +3746,10 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
-      </c>
-      <c r="C238" t="s">
-        <v>245</v>
+        <v>235</v>
+      </c>
+      <c r="C238" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -3762,10 +3757,10 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
-      </c>
-      <c r="C239" t="s">
-        <v>246</v>
+        <v>236</v>
+      </c>
+      <c r="C239" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -3773,10 +3768,10 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
-      </c>
-      <c r="C240" t="s">
-        <v>245</v>
+        <v>237</v>
+      </c>
+      <c r="C240" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -3784,10 +3779,10 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
-      </c>
-      <c r="C241" t="s">
-        <v>246</v>
+        <v>238</v>
+      </c>
+      <c r="C241" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -3795,10 +3790,10 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
-      </c>
-      <c r="C242" t="s">
-        <v>246</v>
+        <v>239</v>
+      </c>
+      <c r="C242" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -3806,10 +3801,10 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
-      </c>
-      <c r="C243" t="s">
-        <v>245</v>
+        <v>240</v>
+      </c>
+      <c r="C243" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -3817,10 +3812,10 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
-      </c>
-      <c r="C244" t="s">
-        <v>245</v>
+        <v>241</v>
+      </c>
+      <c r="C244" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Cardiologie/Excel/cardio_15.xlsx
+++ b/Cardiologie/Excel/cardio_15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649007BA-9893-44D7-8318-D0C4960F27F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2876418-9CBD-4804-9EE9-26D0DEFC523F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="493">
   <si>
     <t>La TVP est toujours définie comme une thrombose complète du réseau veineux profond des MI.</t>
   </si>
@@ -770,6 +770,735 @@
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut être partielle ou complète selon l'étendue au réseau veineux profond </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte est limitée à l'étage sous-poplité (sous le genou) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle affecte au contraire le réseau veineux profond poplité ou plus proximal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne une association fréquente avec cette pathologie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'embolie pulmonaire associée est au contraire décrite comme asymptomatique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme ce chiffre d'incidence annuelle dans la population </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il existe également des facteurs non réversibles ou liés au patient (ex: âge, néoplasie) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est au contraire un élément permettant d'estimer la probabilité clinique de TVP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le score de Wells est effectivement un système utilisé pour estimer cette probabilité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un score élevé (≥ 2) indique au contraire une probabilité "probable" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sa spécificité est au contraire décrite comme médiocre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le protocole recommandé pour exclure une TVP chez les patients à faible risque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est explicitement désignée comme l'examen de premier choix pour le diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document liste cette caractéristique comme une limite de l'examen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle se manifeste par une douleur et un cordon rouge et induré sur le trajet veineux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le nom de la présentation classique de la thrombose veineuse profonde </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle entraîne au contraire une dilatation du réseau superficiel par suppléance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome post-thrombotique est listé comme l'une des complications majeures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le score simplifié ne comporte au contraire que deux niveaux (peu probable ou probable) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un cancer actif confère effectivement un point supplémentaire dans ce score </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'échographie a au contraire une excellente sensibilité (&gt;95%) pour la forme proximale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette forme grave (phlébite bleue) impose effectivement un traitement immédiat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte décrit précisément ces signes comme des séquelles de la TVP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il n'est au contraire pas recommandé de doser les D-dimères si le score est ≥ 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que l'âge est une cause fréquente de résultats positifs sans TVP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'un des deux moyens thérapeutiques essentiels cités </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La forme proximale est plus grave car plus fréquemment associée à l'embolie pulmonaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La grossesse et le post-partum sont des facteurs de risque réversibles identifiés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document les classe effectivement parmi les facteurs de risque réversibles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les longs voyages sont au contraire considérés comme un facteur de risque de stase </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document le classe au contraire parmi les facteurs de risque réversibles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont au contraire classés dans les facteurs non réversibles ou liés au patient </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut être iatrogène ou survenir sur des varices indépendamment d'une TVP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise que la coloration cyanique de la TVP diffère de l'érythème de l'érysipèle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte ne mentionne pas que la TVP elle-même est souvent asymptomatique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme ce lien statistique étroit entre les deux manifestations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont au contraire classées parmi les facteurs non réversibles ou liés au patient </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces signes sont effectivement listés parmi les manifestations cliniques du syndrome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leur spécificité est au contraire décrite comme médiocre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sa détection est au contraire décrite comme plus difficile pour les formes distales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document cite effectivement ces complications trophiques (dont la dermite ocre) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'incidence de la TVP (1/1000) est au contraire le double de celle de l'embolie (0,5/1000) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement repose sur l'anticoagulation ET la contention veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise au contraire que ses indications sont très limitées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme effectivement que les indications chirurgicales sont très réduites </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition anatomique exacte fournie par le document </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces deux critères sont effectivement classés comme facteurs de risque élevé de récidive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mobilisation n'est recommandée qu'après la mise en place de l'anticoagulation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une durée de 3 mois est nécessaire si le risque de récidive est au contraire élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document souligne l'importance d'une compression rapide pour traiter cette forme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle comprend des bandages adhésifs si l'oedème est important et/ou des bas de contention graduée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document suggère d'envisager de poursuivre le traitement (au-delà de 3 mois) dans ce cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils ne nécessitent effectivement pas de contrôles sanguins ni d'ajustement des doses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le protocole recommandé pour exclure une TVP chez les patients à faible probabilité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement par contention et mobilisation est cité spécifiquement pour le flutter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette intervention est au contraire réservée à des indications très spécifiques (CI aux anticoagulants, etc.) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les symptômes surviennent effectivement entre 6 mois et 2 ans après l'épisode </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic repose essentiellement sur l'anamnèse, la clinique et le Doppler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle entraîne au contraire des signes bilatéraux d’emblée dans la plupart des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La compression extrinsèque par une tumeur est citée comme une étiologie possible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut aussi être causée par un cathéter ou certaines thrombophilies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document liste effectivement les douleurs cervicales et le gonflement comme signes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objectif est d'éviter l'extension, de prévenir l'EP, le syndrome post-thrombotique et les récidives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme que ces médicaments sont éliminés essentiellement par voie rénale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses indications doivent au contraire rester exceptionnelles en raison du risque hémorragique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome survient dans les 6 mois à 2 ans après une TVP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'origine néoplasique (rein) est citée comme une étiologie possible bien que plus rare </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les cathéters sont une cause, mais la compression extrinsèque (tumeurs) en est une autre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement anticoagulant est également nécessaire pour les TVP distales (durée variable) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise qu'ils interfèrent effectivement avec certains médicaments </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'anticoagulation est le moyen thérapeutique principal pour tous les types de TVP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est effectivement le plus souvent causée par l'extension d’un thrombus iliaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le cathétérisme veineux est cité comme une cause iatrogène de TVS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que la TVS survient sur des varices dans 75 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise qu'une thrombophlébite peut survenir sur une veine saine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le cordon sur le trajet veineux prend au contraire un aspect rouge et induré </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hyperthermie locale est effectivement un signe clinique de la TVS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’échographie-Doppler permet effectivement d’apprécier l’extension de la thrombose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le passage au réseau veineux profond via les veines perforantes est une complication possible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On utilise au contraire des anti-inflammatoires non stéroïdiens (AINS) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La contention et la mobilisation sont au contraire décrites comme essentielles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un traitement anticoagulant est au contraire souvent proposé pour les formes étendues </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On utilise des anti-inflammatoires non stéroïdiens pour le traitement symptomatique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette indication est effectivement retenue pour prévenir l'extension au réseau profond </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans 25 % des cas, elle survient au contraire sur des veines saines </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition de la thrombose veineuse profonde (TVP) et non superficielle (TVS) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La thrombose poplitée est au contraire classée comme une TVP proximale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les thromboses distales sont effectivement limitées à l’étage sous-poplité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toutes ces veines appartiennent effectivement au territoire des TVP proximales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne une association fréquente entre ces deux pathologies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme ce lien statistique pour les TVP proximales symptomatiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle regroupe au contraire la TVP et l’embolie pulmonaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seulement 50-70% (et non tous) des patients avec EP ont une TVP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est effectivement l'affection la plus fréquente après ces deux pathologies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme ce chiffre d'incidence pour la population générale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle regroupe l'anomalie du flux, de la paroi et de la composition du sang </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est au contraire indispensable pour déterminer la durée du traitement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'anomalie du flux sanguin (stase veineuse) est une composante de la triade de Virchow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions pariétales (anomalies de la paroi) sont une composante de la triade de Virchow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle fait partie de la triade de Virchow (anomalie de la composition chimique du sang) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont classés parmi les facteurs de risque réversibles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est classée dans les facteurs non réversibles ou liés au patient </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On recherche un déficit en protéines C ou S, pas un excès </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'hyperhomocystéinémie qui est un facteur de risque, pas l'hypo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces anomalies de l'hémostase sont des facteurs de risque listés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont les trois types de modifications induisant une thrombose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces pathologies sont citées comme exemples d'anomalies de l'hémostase (Triade 3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'âge avancé est listé comme un facteur de risque lié au patient </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une immobilisation transitoire ou réversible est un facteur de faible risque de récidive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présentation classique est la phlegmatia alba dolens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition du signe de Homans mentionnée dans le document </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'oedème est typiquement unilatéral ou asymétrique, pas bilatéral </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'oedème peut effectivement toucher tout le membre inférieur </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la description de la présentation clinique classique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur peut siéger à la face interne de la cuisse, pas externe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La température systémique élevée (fièvre) peut être le seul signe, pas l'hyperthermie locale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La circulation superficielle supplée le réseau profond obstrué </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'érythrocyanose est décrite comme étant déclive (position pendante) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le diagnostic différentiel de la phlegmatia alba dolens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition clinique de la phlegmatia caerulea dolens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La complication majeure de la TVP est l'embolie pulmonaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle s'accompagne de signes inflammatoires et d'une hyperthermie locale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est due à une thrombose proximale extensive, pas distale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une localisation fréquente des ulcères post-thrombotiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la phlegmatia caerulea dolens qui entraîne un blocage artériel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'un des critères rapportant un point dans le score de Wells simplifié </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mesure se fait 10 cm sous la tubérosité tibiale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'alitement doit durer plus de 3 jours pour valoir un point </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La TVP est considérée comme peu probable si le score est de 0 ou 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On doit soustraire 2 points, pas un seul </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce signe clinique vaut effectivement un point dans le score simplifié </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est un facteur de risque comptant pour un point dans le score </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un antécédent documenté de TVP rapporte un point </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le gonflement généralisé ou du mollet (&gt; 3 cm) valent chacun un point </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les varices simples ne figurent pas dans la liste des critères du score </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce signe clinique rapporte un point dans le calcul du score </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présence de collatérales superficielles vaut un point </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces conditions ne rapportent qu'un seul point, pas deux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La sensibilité et la spécificité varient selon la qualité du test </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si la sensibilité est bonne, la spécificité est au contraire décrite comme médiocre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces facteurs peuvent causer des résultats faussement positifs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il sert uniquement à exclure une TVP, pas à la confirmer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certains anticoagulants oraux directs nécessitent un pré-traitement par HBPM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'étape recommandée si la probabilité clinique est faible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La combinaison d'un score faible et de D-dimères normaux permet l'exclusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un résultat positif impose de passer à l'échographie, quel que soit le score initial </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On passe directement à l'échographie sans doser les D-dimères </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'échographie est l'examen de choix dès que la probabilité est élevée (score ≥ 2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen est très fiable pour les formes proximales (fiabilité &gt; 95 %) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objectif est d'éviter l'extension de la thrombose, les embolies et le syndrome post-thrombotique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont les deux moyens thérapeutiques essentiels cités </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'amélioration des symptômes est au contraire l'un des premiers objectifs mentionnés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une TVP sous le genou est au contraire définie comme une TVP distale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette recommandation de traitement court s'applique à la TVP distale et non proximale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est effectivement une option de prise en charge pour la TVP distale à faible risque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont effectivement classées comme étant à risque de récidive élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est au contraire le sexe masculin qui est cité comme facteur de risque élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La bilatéralité de l'atteinte est effectivement un critère de risque élevé de récidive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document préconise effectivement une anticoagulation de 3 mois dans cette situation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On utilise au contraire préférentiellement de l'héparine de bas poids moléculaire (HBPM) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les TVP idiopathiques (non provoquées) sont au contraire classées à risque élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document stipule une durée minimale de 3 mois d’anticoagulation pour les formes proximales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est effectivement l'explication pathogénique donnée pour ces séquelles permanentes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle doit être débutée dans les 24 heures (et non 12h) pour être considérée comme immédiate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que cette thérapie aide effectivement à la régression des symptômes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle contribue au contraire à la réduction de l’incidence de ce syndrome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les bandages adhésifs de type Tensoplast sont recommandés en cas d'oedème important </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la pression exacte spécifiée par le document pour ce type de bas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leur action est définie par le nombre de deniers et non par une pression fixe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document cite des valeurs de 70 ou 140 deniers pour ces bas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression pour la classe III (forte) est de 34 à 46 mm Hg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la pression exacte mentionnée pour la classe IV (très forte) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression pour la classe A est au contraire de 10-14 mm Hg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pression pour la classe II (moyenne) est de 23 à 32 mm Hg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mobilisation est préconisée dès que l'anticoagulation du patient est efficace </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seules les TVP distales à risque de récidive élevé nécessitent 3 mois de traitement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont classées à risque faible car le facteur de risque majeur est résolu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un alitement court (&lt; 3 jours) est au contraire classé en risque intermédiaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont à faible risque une fois que la fracture est guérie (facteur résolu) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On peut au contraire arrêter l'anticoagulation après 3 mois pour les risques faibles résolus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La chirurgie mineure avec anesthésie de moins de 30 minutes est un risque intermédiaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est au contraire considéré comme un facteur de risque intermédiaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est au contraire classé dans la catégorie de risque intermédiaire (facteur mineur) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'obésité est effectivement listée comme un facteur de risque intermédiaire de récidive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une anesthésie de plus de 30 minutes correspond au contraire à la catégorie de risque faible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont effectivement classées comme un facteur de risque intermédiaire de récidive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est classé comme un risque intermédiaire et non élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce critère concerne la TVP proximale et est effectivement de risque intermédiaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le cancer actif impose une anticoagulation prolongée (&gt; 3 mois), signe d'un risque élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est un facteur majeur non résolu imposant une anticoagulation de plus de 3 mois </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la recommandation pour les patients avec un facteur de risque majeur non résolu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On doit effectivement l'envisager, mais sous réserve d'un faible risque hémorragique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est au contraire classé parmi les facteurs de risque majeurs non résolus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne effectivement cette possibilité pour la catégorie de risque intermédiaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce facteur est classé comme un risque majeur non résolu (anticoagulation &gt; 3 mois) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le dabigatran est un inhibiteur de la thrombine (facteur IIa), pas du facteur Xa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'un des avantages majeurs cités pour les nouveaux anticoagulants oraux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont au contraire des inhibiteurs du facteur Xa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est effectivement requis pour les AVK et certains nouveaux anticoagulants oraux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’insuffisance rénale sévère (clearance &lt; 30ml/min) est une contre-indication aux HBPM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’héparine non fractionnée s’administre au contraire en perfusion I.V. continue </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le taux des plaquettes doit être surveillé tous les 2-3 jours lors du traitement héparinique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’allongement de l’APTT permet effectivement de vérifier l’activité de l’héparine non fractionnée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'activité doit être vérifiée toutes les 6h en cas d'utilisation d'héparine non fractionnée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les AVK débutent le jour même ou le lendemain de l’instauration de l’héparine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’INR cible pour un traitement par AVK est de 2,5 (intervalle 2 - 3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'instauration des AVK nécessite effectivement une couverture initiale par héparine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'apixaban (AOD) est actif d'emblée par voie orale et ne nécessite pas de pré-traitement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement héparinique doit être maintenu jusqu’à obtention d’un INR supérieur à 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'adaptation posologique se fait sur base du contrôle quotidien de l'INR de J3 à J5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les AOD sont actifs d'emblée, au contraire des AVK qui nécessitent un relai </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les AOD sont effectivement préférables aux AVK car ils sont plus efficaces et moins hémorragiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne précise pas le mode d'administration standard des HBPM en perfusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La chirurgie, thrombolyse et filtre cave sont listés comme des "traitements exceptionnels" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La thrombolyse utilise effectivement des schémas à base de ces deux enzymes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il n’y a au contraire pas de démonstration d’un bénéfice pour réduire ce syndrome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle augmente le risque d’hémorragies majeures de 4 fois (et non 2 fois) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la description du profil type pour lequel la thrombolyse est envisagée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement thrombolytique s'accompagne également de contention et mobilisation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le filtre cave a effectivement pour objectif d'empêcher la migration des emboles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’insertion d’un filtre dans la veine cave inférieure est une méthode percutanée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un « caillot flottant » n’est au contraire pas une indication d’emblée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C’est l’une des indications admises pour l'interruption de la VCI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le retrait du filtre doit être rapide dès la résolution de la contre-indication aux anticoagulants </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’interruption est au contraire indiquée en cas de récidives malgré un traitement adapté </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’anticoagulation doit effectivement débuter dès que la contre-indication est levée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La thrombectomie veineuse est indiquée si le membre est en danger </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome post-thrombotique survient au contraire dans les 6 mois à 2 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'oedème est d'abord réversible avant d'évoluer potentiellement vers la chronicité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome s'accompagne au contraire de troubles trophiques (dermite ocre, hypodermite, ulcères) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces différents facteurs physiopathologiques sont effectivement à l'origine du syndrome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic repose au contraire essentiellement sur l’anamnèse, la clinique et le Doppler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les symptômes et signes cliniques sont effectivement similaires à ceux de la TVP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une extension à la veine cave supérieure est effectivement possible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La thrombose veineuse superficielle peut effectivement être iatrogène </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La TVS survient le plus souvent sur le trajet de la saphène interne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme que l'apparition d'une TVS sur veine saine impose cette recherche </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie de Behçet est citée comme pathologie prédisposante pour la TVS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toutes ces catégories de pathologies sont citées comme causes de TVS sur veine saine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présentation clinique inclut effectivement douleur, aspect rouge et hyperthermie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'aspect en "battant de cloche" est effectivement recherché à l'échographie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On propose effectivement un traitement par AVK si les AVK ne sont pas contre-indiqués </t>
+  </si>
+  <si>
+    <t>Page</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G244"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -1122,7 +1851,7 @@
     <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>243</v>
       </c>
@@ -1136,16 +1865,19 @@
         <v>246</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1155,8 +1887,14 @@
       <c r="C2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1166,8 +1904,14 @@
       <c r="C3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1177,8 +1921,14 @@
       <c r="C4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1188,8 +1938,14 @@
       <c r="C5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1199,8 +1955,14 @@
       <c r="C6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1210,8 +1972,14 @@
       <c r="C7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1221,8 +1989,14 @@
       <c r="C8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1232,8 +2006,14 @@
       <c r="C9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1243,8 +2023,14 @@
       <c r="C10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>258</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1254,8 +2040,14 @@
       <c r="C11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>259</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1265,8 +2057,14 @@
       <c r="C12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1276,8 +2074,14 @@
       <c r="C13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1287,8 +2091,14 @@
       <c r="C14" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>262</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1298,8 +2108,14 @@
       <c r="C15" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>263</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1309,8 +2125,14 @@
       <c r="C16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>264</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1320,8 +2142,14 @@
       <c r="C17" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1331,8 +2159,14 @@
       <c r="C18" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>266</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1342,8 +2176,14 @@
       <c r="C19" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>267</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1353,8 +2193,14 @@
       <c r="C20" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>268</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1364,8 +2210,14 @@
       <c r="C21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>269</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1375,8 +2227,14 @@
       <c r="C22" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>270</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1386,8 +2244,14 @@
       <c r="C23" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>271</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1397,8 +2261,14 @@
       <c r="C24" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>272</v>
+      </c>
+      <c r="E24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1408,8 +2278,14 @@
       <c r="C25" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>273</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1419,8 +2295,14 @@
       <c r="C26" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>274</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1430,8 +2312,14 @@
       <c r="C27" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>275</v>
+      </c>
+      <c r="E27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1441,8 +2329,14 @@
       <c r="C28" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>276</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1452,8 +2346,14 @@
       <c r="C29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>277</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1463,8 +2363,14 @@
       <c r="C30" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>278</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1474,8 +2380,14 @@
       <c r="C31" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>279</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1485,8 +2397,14 @@
       <c r="C32" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>280</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1496,8 +2414,14 @@
       <c r="C33" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>281</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1507,8 +2431,14 @@
       <c r="C34" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>282</v>
+      </c>
+      <c r="E34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1518,8 +2448,14 @@
       <c r="C35" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>283</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1529,8 +2465,14 @@
       <c r="C36" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>284</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1540,8 +2482,14 @@
       <c r="C37" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>285</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1551,8 +2499,14 @@
       <c r="C38" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>286</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1562,8 +2516,14 @@
       <c r="C39" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>287</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1573,8 +2533,14 @@
       <c r="C40" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>288</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1584,8 +2550,14 @@
       <c r="C41" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>289</v>
+      </c>
+      <c r="E41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1595,8 +2567,14 @@
       <c r="C42" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>290</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1606,8 +2584,14 @@
       <c r="C43" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>291</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1617,8 +2601,14 @@
       <c r="C44" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>292</v>
+      </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1628,8 +2618,14 @@
       <c r="C45" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>293</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1639,8 +2635,14 @@
       <c r="C46" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>294</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1650,8 +2652,14 @@
       <c r="C47" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>295</v>
+      </c>
+      <c r="E47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1661,8 +2669,14 @@
       <c r="C48" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>296</v>
+      </c>
+      <c r="E48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1672,8 +2686,14 @@
       <c r="C49" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>297</v>
+      </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1683,8 +2703,14 @@
       <c r="C50" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>298</v>
+      </c>
+      <c r="E50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1694,8 +2720,14 @@
       <c r="C51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>299</v>
+      </c>
+      <c r="E51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1705,8 +2737,14 @@
       <c r="C52" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>300</v>
+      </c>
+      <c r="E52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1716,8 +2754,14 @@
       <c r="C53" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>301</v>
+      </c>
+      <c r="E53">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1727,8 +2771,14 @@
       <c r="C54" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>302</v>
+      </c>
+      <c r="E54">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1738,8 +2788,14 @@
       <c r="C55" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>303</v>
+      </c>
+      <c r="E55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1749,8 +2805,14 @@
       <c r="C56" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>304</v>
+      </c>
+      <c r="E56">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1760,8 +2822,14 @@
       <c r="C57" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>305</v>
+      </c>
+      <c r="E57">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1771,8 +2839,14 @@
       <c r="C58" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>293</v>
+      </c>
+      <c r="E58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1782,8 +2856,14 @@
       <c r="C59" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>306</v>
+      </c>
+      <c r="E59">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1793,8 +2873,14 @@
       <c r="C60" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>307</v>
+      </c>
+      <c r="E60">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1804,8 +2890,14 @@
       <c r="C61" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>308</v>
+      </c>
+      <c r="E61">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1815,8 +2907,14 @@
       <c r="C62" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>309</v>
+      </c>
+      <c r="E62">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1826,8 +2924,14 @@
       <c r="C63" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>310</v>
+      </c>
+      <c r="E63">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1837,8 +2941,14 @@
       <c r="C64" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>311</v>
+      </c>
+      <c r="E64">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1848,8 +2958,14 @@
       <c r="C65" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>312</v>
+      </c>
+      <c r="E65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1859,8 +2975,14 @@
       <c r="C66" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>313</v>
+      </c>
+      <c r="E66">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1870,8 +2992,14 @@
       <c r="C67" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>314</v>
+      </c>
+      <c r="E67">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1881,8 +3009,14 @@
       <c r="C68" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>315</v>
+      </c>
+      <c r="E68">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1892,8 +3026,14 @@
       <c r="C69" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>316</v>
+      </c>
+      <c r="E69">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1903,8 +3043,14 @@
       <c r="C70" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>317</v>
+      </c>
+      <c r="E70">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1914,8 +3060,14 @@
       <c r="C71" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>318</v>
+      </c>
+      <c r="E71">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1925,8 +3077,14 @@
       <c r="C72" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>319</v>
+      </c>
+      <c r="E72">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1936,8 +3094,14 @@
       <c r="C73" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>320</v>
+      </c>
+      <c r="E73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1947,8 +3111,14 @@
       <c r="C74" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>321</v>
+      </c>
+      <c r="E74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1958,8 +3128,14 @@
       <c r="C75" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>322</v>
+      </c>
+      <c r="E75">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1969,8 +3145,14 @@
       <c r="C76" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>323</v>
+      </c>
+      <c r="E76">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1980,8 +3162,14 @@
       <c r="C77" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>324</v>
+      </c>
+      <c r="E77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1991,8 +3179,14 @@
       <c r="C78" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>325</v>
+      </c>
+      <c r="E78">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2002,8 +3196,14 @@
       <c r="C79" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>326</v>
+      </c>
+      <c r="E79">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2013,8 +3213,14 @@
       <c r="C80" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>327</v>
+      </c>
+      <c r="E80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2024,8 +3230,14 @@
       <c r="C81" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>328</v>
+      </c>
+      <c r="E81">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2035,8 +3247,14 @@
       <c r="C82" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>329</v>
+      </c>
+      <c r="E82">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2046,8 +3264,14 @@
       <c r="C83" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>330</v>
+      </c>
+      <c r="E83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2057,8 +3281,14 @@
       <c r="C84" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>331</v>
+      </c>
+      <c r="E84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2068,8 +3298,14 @@
       <c r="C85" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>332</v>
+      </c>
+      <c r="E85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2079,8 +3315,14 @@
       <c r="C86" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>333</v>
+      </c>
+      <c r="E86">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2090,8 +3332,14 @@
       <c r="C87" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>334</v>
+      </c>
+      <c r="E87">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2101,8 +3349,14 @@
       <c r="C88" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>335</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2112,8 +3366,14 @@
       <c r="C89" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>336</v>
+      </c>
+      <c r="E89">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2123,8 +3383,14 @@
       <c r="C90" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>337</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2134,8 +3400,14 @@
       <c r="C91" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>338</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2145,8 +3417,14 @@
       <c r="C92" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>339</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2156,8 +3434,14 @@
       <c r="C93" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>340</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2167,8 +3451,14 @@
       <c r="C94" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>341</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2178,8 +3468,14 @@
       <c r="C95" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>342</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2189,8 +3485,14 @@
       <c r="C96" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>343</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2200,8 +3502,14 @@
       <c r="C97" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>344</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2211,8 +3519,14 @@
       <c r="C98" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>345</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -2222,8 +3536,14 @@
       <c r="C99" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>346</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -2233,8 +3553,14 @@
       <c r="C100" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>347</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -2244,8 +3570,14 @@
       <c r="C101" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>348</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -2255,8 +3587,14 @@
       <c r="C102" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>349</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -2266,8 +3604,14 @@
       <c r="C103" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>350</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -2277,8 +3621,14 @@
       <c r="C104" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>351</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -2288,8 +3638,14 @@
       <c r="C105" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>352</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -2299,8 +3655,14 @@
       <c r="C106" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>353</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -2310,8 +3672,14 @@
       <c r="C107" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>354</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -2321,8 +3689,14 @@
       <c r="C108" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>355</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -2332,8 +3706,14 @@
       <c r="C109" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>356</v>
+      </c>
+      <c r="E109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -2343,8 +3723,14 @@
       <c r="C110" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>357</v>
+      </c>
+      <c r="E110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -2354,8 +3740,14 @@
       <c r="C111" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>358</v>
+      </c>
+      <c r="E111">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -2365,8 +3757,14 @@
       <c r="C112" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>359</v>
+      </c>
+      <c r="E112">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -2376,8 +3774,14 @@
       <c r="C113" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>360</v>
+      </c>
+      <c r="E113">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -2387,8 +3791,14 @@
       <c r="C114" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>361</v>
+      </c>
+      <c r="E114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -2398,8 +3808,14 @@
       <c r="C115" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>362</v>
+      </c>
+      <c r="E115">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -2409,8 +3825,14 @@
       <c r="C116" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>363</v>
+      </c>
+      <c r="E116">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -2420,8 +3842,14 @@
       <c r="C117" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>364</v>
+      </c>
+      <c r="E117">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -2431,8 +3859,14 @@
       <c r="C118" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>365</v>
+      </c>
+      <c r="E118">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -2442,8 +3876,14 @@
       <c r="C119" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>366</v>
+      </c>
+      <c r="E119">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -2453,8 +3893,14 @@
       <c r="C120" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>367</v>
+      </c>
+      <c r="E120">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -2464,8 +3910,14 @@
       <c r="C121" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>368</v>
+      </c>
+      <c r="E121">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -2475,8 +3927,14 @@
       <c r="C122" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>369</v>
+      </c>
+      <c r="E122">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -2486,8 +3944,14 @@
       <c r="C123" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>370</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -2497,8 +3961,14 @@
       <c r="C124" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>371</v>
+      </c>
+      <c r="E124">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -2508,8 +3978,14 @@
       <c r="C125" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>372</v>
+      </c>
+      <c r="E125">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -2519,8 +3995,14 @@
       <c r="C126" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>373</v>
+      </c>
+      <c r="E126">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -2530,8 +4012,14 @@
       <c r="C127" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>374</v>
+      </c>
+      <c r="E127">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -2541,8 +4029,14 @@
       <c r="C128" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>375</v>
+      </c>
+      <c r="E128">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -2552,8 +4046,14 @@
       <c r="C129" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>376</v>
+      </c>
+      <c r="E129">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -2563,8 +4063,14 @@
       <c r="C130" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>377</v>
+      </c>
+      <c r="E130">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -2574,8 +4080,14 @@
       <c r="C131" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>378</v>
+      </c>
+      <c r="E131">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -2585,8 +4097,14 @@
       <c r="C132" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>379</v>
+      </c>
+      <c r="E132">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -2596,8 +4114,14 @@
       <c r="C133" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>380</v>
+      </c>
+      <c r="E133">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -2607,8 +4131,14 @@
       <c r="C134" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>381</v>
+      </c>
+      <c r="E134">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -2618,8 +4148,14 @@
       <c r="C135" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>382</v>
+      </c>
+      <c r="E135">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -2629,8 +4165,14 @@
       <c r="C136" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>383</v>
+      </c>
+      <c r="E136">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -2640,8 +4182,14 @@
       <c r="C137" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>384</v>
+      </c>
+      <c r="E137">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -2651,8 +4199,14 @@
       <c r="C138" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>385</v>
+      </c>
+      <c r="E138">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -2662,8 +4216,14 @@
       <c r="C139" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>386</v>
+      </c>
+      <c r="E139">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -2673,8 +4233,14 @@
       <c r="C140" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>387</v>
+      </c>
+      <c r="E140">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -2684,8 +4250,14 @@
       <c r="C141" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>388</v>
+      </c>
+      <c r="E141">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -2695,8 +4267,14 @@
       <c r="C142" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>389</v>
+      </c>
+      <c r="E142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -2706,8 +4284,14 @@
       <c r="C143" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>390</v>
+      </c>
+      <c r="E143">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -2717,8 +4301,14 @@
       <c r="C144" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>391</v>
+      </c>
+      <c r="E144">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -2728,8 +4318,14 @@
       <c r="C145" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>392</v>
+      </c>
+      <c r="E145">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -2739,8 +4335,14 @@
       <c r="C146" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>393</v>
+      </c>
+      <c r="E146">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -2750,8 +4352,14 @@
       <c r="C147" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>394</v>
+      </c>
+      <c r="E147">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -2761,8 +4369,14 @@
       <c r="C148" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>395</v>
+      </c>
+      <c r="E148">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -2772,8 +4386,14 @@
       <c r="C149" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>396</v>
+      </c>
+      <c r="E149">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -2783,8 +4403,14 @@
       <c r="C150" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>397</v>
+      </c>
+      <c r="E150">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -2794,8 +4420,14 @@
       <c r="C151" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>398</v>
+      </c>
+      <c r="E151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -2805,8 +4437,14 @@
       <c r="C152" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>399</v>
+      </c>
+      <c r="E152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -2816,8 +4454,14 @@
       <c r="C153" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>400</v>
+      </c>
+      <c r="E153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -2827,8 +4471,14 @@
       <c r="C154" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>401</v>
+      </c>
+      <c r="E154">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -2838,8 +4488,14 @@
       <c r="C155" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>402</v>
+      </c>
+      <c r="E155">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -2849,8 +4505,14 @@
       <c r="C156" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>403</v>
+      </c>
+      <c r="E156">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -2860,8 +4522,14 @@
       <c r="C157" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>404</v>
+      </c>
+      <c r="E157">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -2871,8 +4539,14 @@
       <c r="C158" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>405</v>
+      </c>
+      <c r="E158">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -2882,8 +4556,14 @@
       <c r="C159" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>406</v>
+      </c>
+      <c r="E159">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -2893,8 +4573,14 @@
       <c r="C160" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>407</v>
+      </c>
+      <c r="E160">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -2904,8 +4590,14 @@
       <c r="C161" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>408</v>
+      </c>
+      <c r="E161">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -2915,8 +4607,14 @@
       <c r="C162" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>409</v>
+      </c>
+      <c r="E162">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -2926,8 +4624,14 @@
       <c r="C163" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>410</v>
+      </c>
+      <c r="E163">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -2937,8 +4641,14 @@
       <c r="C164" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>411</v>
+      </c>
+      <c r="E164">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -2948,8 +4658,14 @@
       <c r="C165" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>412</v>
+      </c>
+      <c r="E165">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -2959,8 +4675,14 @@
       <c r="C166" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" t="s">
+        <v>413</v>
+      </c>
+      <c r="E166">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -2970,8 +4692,14 @@
       <c r="C167" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" t="s">
+        <v>414</v>
+      </c>
+      <c r="E167">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -2981,8 +4709,14 @@
       <c r="C168" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" t="s">
+        <v>415</v>
+      </c>
+      <c r="E168">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -2992,8 +4726,14 @@
       <c r="C169" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169" t="s">
+        <v>416</v>
+      </c>
+      <c r="E169">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -3003,8 +4743,14 @@
       <c r="C170" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" t="s">
+        <v>417</v>
+      </c>
+      <c r="E170">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -3014,8 +4760,14 @@
       <c r="C171" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" t="s">
+        <v>418</v>
+      </c>
+      <c r="E171">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -3025,8 +4777,14 @@
       <c r="C172" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172" t="s">
+        <v>419</v>
+      </c>
+      <c r="E172">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -3036,8 +4794,14 @@
       <c r="C173" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" t="s">
+        <v>420</v>
+      </c>
+      <c r="E173">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -3047,8 +4811,14 @@
       <c r="C174" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" t="s">
+        <v>421</v>
+      </c>
+      <c r="E174">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -3058,8 +4828,14 @@
       <c r="C175" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175" t="s">
+        <v>422</v>
+      </c>
+      <c r="E175">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -3069,8 +4845,14 @@
       <c r="C176" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176" t="s">
+        <v>423</v>
+      </c>
+      <c r="E176">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -3080,8 +4862,14 @@
       <c r="C177" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177" t="s">
+        <v>424</v>
+      </c>
+      <c r="E177">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -3091,8 +4879,14 @@
       <c r="C178" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178" t="s">
+        <v>425</v>
+      </c>
+      <c r="E178">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -3102,8 +4896,14 @@
       <c r="C179" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179" t="s">
+        <v>426</v>
+      </c>
+      <c r="E179">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -3113,8 +4913,14 @@
       <c r="C180" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180" t="s">
+        <v>427</v>
+      </c>
+      <c r="E180">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -3124,8 +4930,14 @@
       <c r="C181" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181" t="s">
+        <v>428</v>
+      </c>
+      <c r="E181">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -3135,8 +4947,14 @@
       <c r="C182" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182" t="s">
+        <v>429</v>
+      </c>
+      <c r="E182">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -3146,8 +4964,14 @@
       <c r="C183" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183" t="s">
+        <v>430</v>
+      </c>
+      <c r="E183">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -3157,8 +4981,14 @@
       <c r="C184" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184" t="s">
+        <v>431</v>
+      </c>
+      <c r="E184">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -3168,8 +4998,14 @@
       <c r="C185" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185" t="s">
+        <v>432</v>
+      </c>
+      <c r="E185">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -3179,8 +5015,14 @@
       <c r="C186" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186" t="s">
+        <v>433</v>
+      </c>
+      <c r="E186">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -3190,8 +5032,14 @@
       <c r="C187" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187" t="s">
+        <v>434</v>
+      </c>
+      <c r="E187">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -3201,8 +5049,14 @@
       <c r="C188" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188" t="s">
+        <v>435</v>
+      </c>
+      <c r="E188">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -3212,8 +5066,14 @@
       <c r="C189" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189" t="s">
+        <v>436</v>
+      </c>
+      <c r="E189">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -3223,8 +5083,14 @@
       <c r="C190" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190" t="s">
+        <v>437</v>
+      </c>
+      <c r="E190">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -3234,8 +5100,14 @@
       <c r="C191" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191" t="s">
+        <v>438</v>
+      </c>
+      <c r="E191">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -3245,8 +5117,14 @@
       <c r="C192" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192" t="s">
+        <v>439</v>
+      </c>
+      <c r="E192">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -3256,8 +5134,14 @@
       <c r="C193" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193" t="s">
+        <v>440</v>
+      </c>
+      <c r="E193">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -3267,8 +5151,14 @@
       <c r="C194" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194" t="s">
+        <v>441</v>
+      </c>
+      <c r="E194">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -3278,8 +5168,14 @@
       <c r="C195" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195" t="s">
+        <v>442</v>
+      </c>
+      <c r="E195">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -3289,8 +5185,14 @@
       <c r="C196" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196" t="s">
+        <v>443</v>
+      </c>
+      <c r="E196">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -3300,8 +5202,14 @@
       <c r="C197" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197" t="s">
+        <v>444</v>
+      </c>
+      <c r="E197">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -3311,8 +5219,14 @@
       <c r="C198" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198" t="s">
+        <v>445</v>
+      </c>
+      <c r="E198">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -3322,8 +5236,14 @@
       <c r="C199" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199" t="s">
+        <v>446</v>
+      </c>
+      <c r="E199">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -3333,8 +5253,14 @@
       <c r="C200" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200" t="s">
+        <v>447</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -3344,8 +5270,14 @@
       <c r="C201" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201" t="s">
+        <v>448</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -3355,8 +5287,14 @@
       <c r="C202" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202" t="s">
+        <v>449</v>
+      </c>
+      <c r="E202">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -3366,8 +5304,14 @@
       <c r="C203" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D203" t="s">
+        <v>450</v>
+      </c>
+      <c r="E203">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -3377,8 +5321,14 @@
       <c r="C204" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D204" t="s">
+        <v>451</v>
+      </c>
+      <c r="E204">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -3388,8 +5338,14 @@
       <c r="C205" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D205" t="s">
+        <v>452</v>
+      </c>
+      <c r="E205">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -3399,8 +5355,14 @@
       <c r="C206" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D206" t="s">
+        <v>453</v>
+      </c>
+      <c r="E206">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -3410,8 +5372,14 @@
       <c r="C207" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D207" t="s">
+        <v>454</v>
+      </c>
+      <c r="E207">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -3421,8 +5389,14 @@
       <c r="C208" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D208" t="s">
+        <v>455</v>
+      </c>
+      <c r="E208">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -3432,8 +5406,14 @@
       <c r="C209" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D209" t="s">
+        <v>456</v>
+      </c>
+      <c r="E209">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -3443,8 +5423,14 @@
       <c r="C210" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D210" t="s">
+        <v>457</v>
+      </c>
+      <c r="E210">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -3454,8 +5440,14 @@
       <c r="C211" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D211" t="s">
+        <v>458</v>
+      </c>
+      <c r="E211">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -3465,8 +5457,14 @@
       <c r="C212" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D212" t="s">
+        <v>459</v>
+      </c>
+      <c r="E212">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -3476,8 +5474,14 @@
       <c r="C213" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D213" t="s">
+        <v>460</v>
+      </c>
+      <c r="E213">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -3487,8 +5491,14 @@
       <c r="C214" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D214" t="s">
+        <v>461</v>
+      </c>
+      <c r="E214">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -3498,8 +5508,14 @@
       <c r="C215" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D215" t="s">
+        <v>462</v>
+      </c>
+      <c r="E215">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -3509,8 +5525,14 @@
       <c r="C216" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D216" t="s">
+        <v>463</v>
+      </c>
+      <c r="E216">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -3520,8 +5542,14 @@
       <c r="C217" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D217" t="s">
+        <v>464</v>
+      </c>
+      <c r="E217">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -3531,8 +5559,14 @@
       <c r="C218" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D218" t="s">
+        <v>465</v>
+      </c>
+      <c r="E218">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -3542,8 +5576,14 @@
       <c r="C219" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D219" t="s">
+        <v>466</v>
+      </c>
+      <c r="E219">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -3553,8 +5593,14 @@
       <c r="C220" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D220" t="s">
+        <v>467</v>
+      </c>
+      <c r="E220">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -3564,8 +5610,14 @@
       <c r="C221" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D221" t="s">
+        <v>468</v>
+      </c>
+      <c r="E221">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -3575,8 +5627,14 @@
       <c r="C222" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D222" t="s">
+        <v>469</v>
+      </c>
+      <c r="E222">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -3586,8 +5644,14 @@
       <c r="C223" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D223" t="s">
+        <v>470</v>
+      </c>
+      <c r="E223">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -3597,8 +5661,14 @@
       <c r="C224" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D224" t="s">
+        <v>471</v>
+      </c>
+      <c r="E224">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -3608,8 +5678,14 @@
       <c r="C225" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D225" t="s">
+        <v>472</v>
+      </c>
+      <c r="E225">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -3619,8 +5695,14 @@
       <c r="C226" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D226" t="s">
+        <v>473</v>
+      </c>
+      <c r="E226">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -3630,8 +5712,14 @@
       <c r="C227" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D227" t="s">
+        <v>474</v>
+      </c>
+      <c r="E227">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -3641,8 +5729,14 @@
       <c r="C228" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D228" t="s">
+        <v>475</v>
+      </c>
+      <c r="E228">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -3652,8 +5746,14 @@
       <c r="C229" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D229" t="s">
+        <v>476</v>
+      </c>
+      <c r="E229">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -3663,8 +5763,14 @@
       <c r="C230" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D230" t="s">
+        <v>477</v>
+      </c>
+      <c r="E230">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -3674,8 +5780,14 @@
       <c r="C231" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D231" t="s">
+        <v>478</v>
+      </c>
+      <c r="E231">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -3685,8 +5797,14 @@
       <c r="C232" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D232" t="s">
+        <v>479</v>
+      </c>
+      <c r="E232">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -3696,8 +5814,14 @@
       <c r="C233" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D233" t="s">
+        <v>480</v>
+      </c>
+      <c r="E233">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -3707,8 +5831,14 @@
       <c r="C234" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D234" t="s">
+        <v>481</v>
+      </c>
+      <c r="E234">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -3718,8 +5848,14 @@
       <c r="C235" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D235" t="s">
+        <v>482</v>
+      </c>
+      <c r="E235">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -3729,8 +5865,14 @@
       <c r="C236" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D236" t="s">
+        <v>483</v>
+      </c>
+      <c r="E236">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -3740,8 +5882,14 @@
       <c r="C237" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D237" t="s">
+        <v>484</v>
+      </c>
+      <c r="E237">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -3751,8 +5899,14 @@
       <c r="C238" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D238" t="s">
+        <v>485</v>
+      </c>
+      <c r="E238">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -3762,8 +5916,14 @@
       <c r="C239" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D239" t="s">
+        <v>486</v>
+      </c>
+      <c r="E239">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -3773,8 +5933,14 @@
       <c r="C240" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D240" t="s">
+        <v>487</v>
+      </c>
+      <c r="E240">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -3784,8 +5950,14 @@
       <c r="C241" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D241" t="s">
+        <v>488</v>
+      </c>
+      <c r="E241">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -3795,8 +5967,14 @@
       <c r="C242" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D242" t="s">
+        <v>489</v>
+      </c>
+      <c r="E242">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -3806,8 +5984,14 @@
       <c r="C243" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D243" t="s">
+        <v>490</v>
+      </c>
+      <c r="E243">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -3816,6 +6000,12 @@
       </c>
       <c r="C244" t="b">
         <v>0</v>
+      </c>
+      <c r="D244" t="s">
+        <v>491</v>
+      </c>
+      <c r="E244">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
